--- a/output/pdf_financials_xlsx/NOM.xlsx
+++ b/output/pdf_financials_xlsx/NOM.xlsx
@@ -2195,16 +2195,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.686874</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.733369</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.233565</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.333325</v>
       </c>
     </row>
     <row r="93">
@@ -3688,7 +3688,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -4242,7 +4246,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>1.686874</v>
       </c>

--- a/output/pdf_financials_xlsx/NOM.xlsx
+++ b/output/pdf_financials_xlsx/NOM.xlsx
@@ -639,13 +639,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.002892</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000648</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00145</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -940,13 +940,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-5.440935</v>
+        <v>-5.443827</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.392854</v>
+        <v>-2.393502</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.053427</v>
+        <v>-2.054877</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-8.084172000000001</v>
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-5.403735</v>
+        <v>-5.406627</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.355654</v>
+        <v>-2.356302</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.053427</v>
+        <v>-2.054877</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-8.059289</v>
@@ -1077,16 +1077,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.024507</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.005112</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.95787</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>18.230547</v>
       </c>
     </row>
     <row r="35">
@@ -1115,16 +1115,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.024507</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.005112</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.95787</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>18.230547</v>
       </c>
     </row>
     <row r="37">
@@ -1343,16 +1343,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.062554</v>
+        <v>0.038047</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.007112</v>
+        <v>0.002</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.127047</v>
+        <v>0.169177</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>18.239837</v>
+        <v>0.00929</v>
       </c>
     </row>
     <row r="49">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">

--- a/output/pdf_financials_xlsx/NOM.xlsx
+++ b/output/pdf_financials_xlsx/NOM.xlsx
@@ -667,7 +667,7 @@
         <v>-0</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>0.125579</v>
       </c>
     </row>
     <row r="14">
@@ -949,7 +949,7 @@
         <v>-2.054877</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-8.084172000000001</v>
+        <v>-8.209751000000001</v>
       </c>
     </row>
     <row r="28">
@@ -987,7 +987,7 @@
         <v>-2.054877</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-8.059289</v>
+        <v>-8.184868</v>
       </c>
     </row>
     <row r="30">
@@ -6874,7 +6874,11 @@
           <t>Debt financing costs 8</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NOM.xlsx
+++ b/output/pdf_financials_xlsx/NOM.xlsx
@@ -1655,16 +1655,16 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.24265</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.445755</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.63098</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.40442</v>
       </c>
     </row>
     <row r="65">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.0585</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.224758</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.044676</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="68">
@@ -2531,10 +2531,10 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.040147</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.308801</v>
       </c>
     </row>
     <row r="111">
@@ -4318,7 +4318,11 @@
           <t>Accretion expenses</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
